--- a/artfynd/A 24670-2025 artfynd.xlsx
+++ b/artfynd/A 24670-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90000677</v>
+        <v>90000680</v>
       </c>
       <c r="B2" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464711.7561093902</v>
+        <v>464768</v>
       </c>
       <c r="R2" t="n">
-        <v>6926455.492714526</v>
+        <v>6926513</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90000684</v>
+        <v>90000683</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464814.9353736756</v>
+        <v>464823</v>
       </c>
       <c r="R3" t="n">
-        <v>6926573.764048883</v>
+        <v>6926552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90000683</v>
+        <v>90000681</v>
       </c>
       <c r="B4" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464823.0492477226</v>
+        <v>464790</v>
       </c>
       <c r="R4" t="n">
-        <v>6926552.397012566</v>
+        <v>6926518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90000678</v>
+        <v>90000679</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464765.335209145</v>
+        <v>464779</v>
       </c>
       <c r="R5" t="n">
-        <v>6926483.610113881</v>
+        <v>6926487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90000711</v>
+        <v>90000684</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464802.1295014112</v>
+        <v>464815</v>
       </c>
       <c r="R6" t="n">
-        <v>6926545.67833171</v>
+        <v>6926574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1253,22 +1178,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kajsa Mattsson</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90000681</v>
+        <v>90000711</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464790.2548225657</v>
+        <v>464802</v>
       </c>
       <c r="R7" t="n">
-        <v>6926518.045227126</v>
+        <v>6926546</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1370,44 +1280,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90000680</v>
+        <v>90000677</v>
       </c>
       <c r="B8" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464768.4229463509</v>
+        <v>464712</v>
       </c>
       <c r="R8" t="n">
-        <v>6926512.724257505</v>
+        <v>6926455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,19 +1355,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90000679</v>
+        <v>90000674</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220075</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464778.8089833452</v>
+        <v>464712</v>
       </c>
       <c r="R9" t="n">
-        <v>6926487.168857198</v>
+        <v>6926429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,19 +1457,9 @@
           <t>2020-06-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1608,6 +1488,312 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>90000676</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storhågna - Rätan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>464695</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6926443</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Calluna AB (EEN0020).</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>90000710</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storhågna - Rätan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>464687</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6926450</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Calluna AB (EEN0020).</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kajsa Mattsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>90000678</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storhågna - Rätan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>464765</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6926484</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Calluna AB (EEN0020).</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
